--- a/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
+++ b/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/monitor/axi_monitor_base.sv:483-485</t>
+          <t>rtl/amba/monitor/axi_monitor_base.sv:697-701</t>
         </is>
       </c>
     </row>
@@ -1253,14 +1253,14 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/monitor/axi_monitor_base.sv:456-485, rtl/amba/includes/monitor_common_pkg.sv:114-116, projects/components/dmas/stream/rtl/macro/stream_core.sv:73-74</t>
+          <t>rtl/amba/monitor/axi_monitor_base.sv:656-701, rtl/amba/includes/monitor_common_pkg.sv:115-132, projects/components/dmas/stream/rtl/macro/stream_core.sv:125-129</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>The reopen threshold sits STRICTLY ABOVE the command cap (67 &gt; 66): even a table whose command entries are all permanently in flight recovers block_ready as soon as orphan entries drain. The old flat MAX-3 margin parked the table exactly AT the threshold and never re-asserted (stream_core multi-channel wedge). Undersizing MAX_TRANSACTIONS on purpose (mon_small config) therefore throttles-and-recovers, never deadlocks.</t>
+          <t>The reopen threshold sits STRICTLY ABOVE the command cap (69 &gt; 68): even a table whose command entries are all permanently in flight recovers block_ready as soon as orphan entries drain. The old flat MAX-3 margin parked the table exactly AT the threshold and never re-asserted (stream_core multi-channel wedge). Undersizing MAX_TRANSACTIONS on purpose (mon_small config) therefore throttles-and-recovers, never deadlocks.</t>
         </is>
       </c>
     </row>
@@ -1289,12 +1289,12 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>NUM_CHANNELS * AR_MAX_OUTSTANDING + 4</t>
+          <t>max(16, NUM_CHANNELS * AR_MAX_OUTSTANDING + MON_TRANS_MARGIN)</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>(MAX &gt;= 16) ? 2 : 0</t>
+          <t>(MAX &gt;= 16) ? 4 : 0</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>&gt;= 67</t>
+          <t>&gt;= 69</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>&lt; 67</t>
+          <t>&lt; 69</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E213"/>
+  <dimension ref="A1:E243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D199" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1115-1123</t>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1118-1126</t>
         </is>
       </c>
     </row>
@@ -6809,6 +6809,431 @@
       <c r="C213" s="4" t="inlineStr">
         <is>
           <t>see exit-decision maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>run-base generator: TERMS</t>
+        </is>
+      </c>
+      <c r="D216" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1021-1062, projects/components/misc/rtl/stream_run_addr_gen.sv:152-221</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="7" t="inlineStr">
+        <is>
+          <t>u_rd_addr_gen / u_wr_addr_gen are instantiated per direction; the block is shared with RAPIDS, so an RTL change has two consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="C218" s="3" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>chan_reset</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>r_channel_reset_active (registered cfg_channel_reset)</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:440</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>w_addrgen_start -&gt; stream_run_addr_gen.start</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1030</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="inlineStr">
+        <is>
+          <t>fifo_nonempty</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>o_base_valid (i_addr_fifo rd_valid)</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/misc/rtl/stream_run_addr_gen.sv:217</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="inlineStr">
+        <is>
+          <t>gen_rst</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>i_addr_fifo.axi_aresetn == rst_n (BLOCK reset)</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/misc/rtl/stream_run_addr_gen.sv:213</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>run-base generator: INVARIANTS</t>
+        </is>
+      </c>
+      <c r="D225" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1029, projects/components/misc/rtl/stream_run_addr_gen.sv:152</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="7" t="inlineStr">
+        <is>
+          <t>I1 and I2 do not EXCLUDE the hazard rows below -- they produce them. That is the finding, not a footnote.</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>invariant</t>
+        </is>
+      </c>
+      <c r="C227" s="3" t="inlineStr">
+        <is>
+          <t>citation</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>consequence for the table</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>I1</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>channel reset NEVER reaches the generator: .rst_n is wired to the block reset, not r_channel_reset_active</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1029, :1051</t>
+        </is>
+      </c>
+      <c r="D228" s="4" t="inlineStr">
+        <is>
+          <t>chan_reset cannot empty i_addr_fifo</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="inlineStr">
+        <is>
+          <t>I2</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>start re-arms the WALKER only (r_inner_count, r_gen_beats, indices); it does not clear i_addr_fifo</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/misc/rtl/stream_run_addr_gen.sv:152</t>
+        </is>
+      </c>
+      <c r="D229" s="4" t="inlineStr">
+        <is>
+          <t>a new descriptor generates BEHIND whatever is still queued</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>I3</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>i_addr_fifo depth is 4 per direction</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1025, projects/components/misc/rtl/stream_run_addr_gen.sv:210</t>
+        </is>
+      </c>
+      <c r="D230" s="4" t="inlineStr">
+        <is>
+          <t>bounds the stale-base exposure at 4 addresses per direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>run-base generator: DECISION TABLE (FIFO content at next start)</t>
+        </is>
+      </c>
+      <c r="D233" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1021-1062, projects/components/misc/rtl/stream_run_addr_gen.sv:152-221</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="7" t="inlineStr">
+        <is>
+          <t>NO row is ILLEGAL: every combination is reachable, so nothing structurally prevents the stale-base case -- it is bounded (4 per direction), not excluded. Severity is low because w_addrgen_start only pulses for EXT descriptors (projects/components/dmas/stream/rtl/fub/scheduler.sv:1030) and channel reset mid-generation is rare. A gaxi_drop_fifo_sync drop_all flush-on-start was attempted and reverted after it regressed working cases on a flush/read timing interaction; that attempt was never committed, so it cannot be inspected. Note gaxi_drop_fifo_sync blocks normal read/write for the duration of a drop, which is the likely mechanism. Documented rather than fixed: see STREAM TASK-058.</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>chan_reset</t>
+        </is>
+      </c>
+      <c r="B235" s="3" t="inlineStr">
+        <is>
+          <t>start</t>
+        </is>
+      </c>
+      <c r="C235" s="3" t="inlineStr">
+        <is>
+          <t>fifo_nonempty</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>verdict</t>
+        </is>
+      </c>
+      <c r="E235" s="3" t="inlineStr">
+        <is>
+          <t>behaviour / excluded by</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C236" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D236" s="4" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="E236" s="4" t="inlineStr">
+        <is>
+          <t>idle, nothing queued</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B237" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C237" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D237" s="4" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="E237" s="4" t="inlineStr">
+        <is>
+          <t>normal drain: consumer pops generated bases</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B238" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D238" s="4" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="E238" s="4" t="inlineStr">
+        <is>
+          <t>intended case - start on an empty FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B239" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D239" s="4" t="inlineStr">
+        <is>
+          <t>legal (benign)</t>
+        </is>
+      </c>
+      <c r="E239" s="4" t="inlineStr">
+        <is>
+          <t>start while this descriptor's own bases are still queued; the walker reloads and appends in order</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C240" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D240" s="4" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="E240" s="4" t="inlineStr">
+        <is>
+          <t>channel reset with an already-empty FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B241" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C241" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D241" s="4" t="inlineStr">
+        <is>
+          <t>HAZARD</t>
+        </is>
+      </c>
+      <c r="E241" s="4" t="inlineStr">
+        <is>
+          <t>reset returns the FSM to CH_IDLE but leaves up to 4 stale bases per direction (I1, I2, I3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B242" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D242" s="4" t="inlineStr">
+        <is>
+          <t>legal</t>
+        </is>
+      </c>
+      <c r="E242" s="4" t="inlineStr">
+        <is>
+          <t>reset then restart with an empty FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B243" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D243" s="4" t="inlineStr">
+        <is>
+          <t>HAZARD</t>
+        </is>
+      </c>
+      <c r="E243" s="4" t="inlineStr">
+        <is>
+          <t>next descriptor generates behind stale bases; the consumer pops the STALE ones first (I1, I2, I3)</t>
         </is>
       </c>
     </row>

--- a/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
+++ b/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,8 +56,16 @@
       <i val="1"/>
       <color rgb="009C6500"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +80,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,6 +137,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -985,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1048,14 +1071,14 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. The AR payload (addr/len/id/user) rides the same handshake but cannot affect whether it completes; the monitor's table contents reach this cone only through block_ready, which is already an axis.</t>
         </is>
       </c>
     </row>
@@ -1131,80 +1154,77 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      core_ready &amp; block_ready  |  core_ready &amp; !mon_enable</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>w_block_ready  (monitor capacity)</t>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>rtl/amba/monitor/axi_monitor_base.sv:697-701</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>block_ready = (MAX_TRANSACTIONS &gt; BLOCK_MARGIN) ? (active_count &lt; MAX_TRANSACTIONS - BLOCK_MARGIN) : 1'b1   [vars: max_gt_margin (param, compile-time), count_below (comparator)]</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = max_gt_margin/count_below   cols = </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: block_ready follows count_below whenever the table is big enough to carry a margin; degenerate tables never block. POLARITY is the loaded gun here: 1 = proceed. The inverted pre-fix polarity deadlocked every upstream handshake at reset.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="9" t="inlineStr">
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two. max_gt_margin is a compile-time comparison of two localparams and count_below folds the whole active_count vs MAX_TRANSACTIONS-BLOCK_MARGIN comparison into one term; nothing else in the monitor reaches this assign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B29" s="11" t="n">
@@ -1214,7 +1234,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>01</t>
         </is>
       </c>
       <c r="B30" s="11" t="n">
@@ -1224,228 +1244,554 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B31" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B32" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: !max_gt_margin  |  count_below</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      !max_gt_margin  |  count_below</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>COMPL packet emission  (monitor cfg -&gt; packet class)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_reporter_compl.sv:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>w_events[idx] = trans_table[idx].valid &amp;&amp; !event_reported[idx] &amp;&amp; (state == TRANS_COMPLETE) &amp;&amp; cfg_compl_enable   [inside generate if (ENABLE_COMPL_LOGIC); else compl_valid = 1'b0]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>rows = build_compl/use_mon   cols = cfg_compl/is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. Each axis is ONE term with its own equation -- that is the point: two axes resolving to the same signal would be visible here, which is exactly the aliasing defect that shipped. The complement is the slot-leak guard: w_auto_retire = !ENABLE_COMPL_LOGIC || !cfg_compl_enable retires a terminal entry when no packet can ever be emitted, so a runtime-disabled class frees its slot instead of wedging the table (rtl/amba/monitor/axi_monitor_reporter.sv:496-497). VERDICT READS 'DIFFERS' ON PURPOSE -- and it is the finding. The derived cover drops use_mon: the invariant below makes cfg_compl=1 imply use_mon=1, so the four use_mon=0 &amp;&amp; cfg_compl=1 cells are X and Quine-McCluskey absorbs them. The RTL's use_mon term is therefore REDUNDANT GIVEN THE INVARIANT -- defence in depth, not logic. It is worth keeping (it makes the monitors-off build independent of the CSR plumbing being correct), but this map is what says so, and if the tie-off at CORE:869 were ever removed the term would stop being redundant and start being load-bearing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>build_compl</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>ENABLE_COMPL_LOGIC &lt;- DATA_MON_ENABLE_COMPL_LOGIC (stream_core parameter, default 1'b0)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:202, :1557</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>use_mon</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>USE_AXI_MONITORS: selects the g_monitors_enabled generate that feeds every int_cfg_*</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:784</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>cfg_compl</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>cfg_compl_enable &lt;- int_cfg_rdeng_mon_compl_enable (= cfg_rdeng_mon_compl_enable when monitors are built)</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:808, :1635</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>is_complete</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>trans_table[idx].state == TRANS_COMPLETE</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_reporter_compl.sv:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    use_mon=0 forces cfg_compl to 0: the g_monitors_disabled arm ties every int_cfg_*_enable to 1'b0, so (use_mon=0, cfg_compl=1) is unreachable, not a 0.</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:869</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) build_compl and cfg_compl are INDEPENDENT -- one is a synthesis parameter, the other a runtime CSR bit, and no RTL relates them. Stated because an aliasing defect would show up here as a relation that HAD to exist.</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:202, :808</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) perf_run is the deliberate exception to the monitors-off tie-off: it passes through to drive the always-on datapath perf window, so monitors-off does NOT zero every cfg signal.</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:883</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. valid &amp;&amp; !event_reported are per-slot bookkeeping orthogonal to the cfg chain (same expression, rtl/amba/monitor/axi_monitor_reporter_compl.sv:51), and the address-filter path retires separately before this cone (rtl/amba/monitor/axi_monitor_reporter.sv:483-489). The other class enables (error/timeout/perf/threshold) drive their own sub-reporters and cannot change COMPL emission. Per-index i is a loop replication, not a variable of the decision.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E58" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: build_compl &amp; cfg_compl &amp; is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      build_compl &amp; use_mon &amp; cfg_compl &amp; is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t>saturation-recovery contract (stream default sizing)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D65" s="5" t="inlineStr">
         <is>
           <t>rtl/amba/monitor/axi_monitor_base.sv:656-701, rtl/amba/includes/monitor_common_pkg.sv:115-132, projects/components/dmas/stream/rtl/macro/stream_core.sv:125-129</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="7" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
         <is>
           <t>The reopen threshold sits STRICTLY ABOVE the command cap (69 &gt; 68): even a table whose command entries are all permanently in flight recovers block_ready as soon as orphan entries drain. The old flat MAX-3 margin parked the table exactly AT the threshold and never re-asserted (stream_core multi-channel wedge). Undersizing MAX_TRANSACTIONS on purpose (mon_small config) therefore throttles-and-recovers, never deadlocks.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>expression</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>8ch default value</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>MAX_TRANSACTIONS</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>max(16, NUM_CHANNELS * AR_MAX_OUTSTANDING + MON_TRANS_MARGIN)</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>cmd_entry_reserve(MAX)</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>(MAX &gt;= 16) ? 4 : 0</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>command-entry cap (trans_mgr)</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>MAX - reserve</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>BLOCK_MARGIN</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
         <is>
           <t>reserve - 1 (or flat 3 if reserve==0)</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C71" s="4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>block threshold</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>block when active_count &gt;= MAX - margin</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>&gt;= 69</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>reopen threshold</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
         <is>
           <t>re-assert when active_count &lt; MAX - margin</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C73" s="4" t="inlineStr">
         <is>
           <t>&lt; 69</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t>monitor enable tie-off (build-level gate)</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:641-732</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>e.g. projects/components/dmas/stream/rtl/macro/stream_core.sv:660 (enabled branch) vs :715 (tied-off branch). The always-on axi_bus_meter perf buckets survive USE_AXI_MONITORS=0 by design - only the heavy monitors and histograms are gated.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>USE_AXI_MONITORS</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>int_cfg_*_mon_enable</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B50" s="4">
+      <c r="B79" s="4">
         <f> cfg_*_mon_enable (CSR)</f>
         <v/>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>runtime on/off; wrapper instantiates the monitor (USE_MONITOR=1)</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B51" s="4">
+      <c r="B80" s="4">
         <f> 1'b0 (tied)</f>
         <v/>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>monitor logic absent, w_block_ready tied 1: bare skid, zero datapath interference</t>
         </is>
@@ -3168,14 +3514,14 @@
     <row r="37">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -3276,14 +3622,14 @@
     <row r="53">
       <c r="A53" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -3401,14 +3747,14 @@
     <row r="69">
       <c r="A69" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -3503,14 +3849,14 @@
     <row r="83">
       <c r="A83" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -3699,7 +4045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3762,14 +4108,14 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -3887,14 +4233,14 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -4099,14 +4445,14 @@
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -4224,14 +4570,14 @@
     <row r="65">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -4328,361 +4674,557 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>assign axi_wr_sram_drain = m_axi_wvalid &amp;&amp; m_axi_wready;</t>
+          <t>axi_wr_sram_drain = m_axi_wvalid &amp;&amp; m_axi_wready, with m_axi_wvalid = r_w_active &amp;&amp; axi_wr_sram_valid[id] &amp;&amp; axi_wr_sram_valid_comb[id]</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = m_axi_wvalid/m_axi_wready   cols = </t>
+          <t>rows = r_w_active/sram_valid_reg   cols = sram_valid_comb/wready</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): pop exactly the beats actually transmitted. BUG FIX (lost-WLAST deadlock): the pre-fix 'r_w_active &amp;&amp; m_axi_wready' form put a 1 in the wvalid=0 column - the beat was consumed but never transmitted, and when it was the burst's final beat WLAST never rode a valid beat and the channel hung (found via the per-channel timing-skew 'mixed' profile, kept as regression sentinel). See projects/components/dmas/stream/known_issues/resolved/axi_write_engine_wlast_drain.md.</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. BUG FIX (lost-WLAST deadlock): the pre-fix 'r_w_active &amp;&amp; m_axi_wready' form put a 1 wherever the SRAM valids were low - the beat was consumed but never transmitted, and when it was the burst's final beat WLAST never rode a valid beat and the channel hung (found via the per-channel timing-skew 'mixed' profile, kept as regression sentinel). See projects/components/dmas/stream/known_issues/resolved/axi_write_engine_wlast_drain.md. NOTE the axes are DECOMPOSED: m_axi_wvalid is itself three terms, and mapping it as one axis would hide the registered-vs-combinational AND that fixes a separate defect (a 1-cycle dry window leaking stale data onto the bus, projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:709-719).</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>r_w_active</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>burst in progress; set on W-phase FIFO pop, cleared on WLAST</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:720</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="9" t="inlineStr">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>sram_valid_reg</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_valid[r_w_channel_id] -- REGISTERED per-channel valid</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:721</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>sram_valid_comb</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>axi_wr_sram_valid_comb[r_w_channel_id] -- COMBINATIONAL valid; filters the 1-cycle dry window the registered one misses</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:722</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>wready</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>m_axi_wready -- downstream W-channel ready (input port)</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:704</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) sram_valid_comb is the combinational view of the same per-channel valid that sram_valid_reg registers, so the registered one cannot be high in a cycle the combinational one was never high in the preceding cycle -- but within a single cycle both orders occur, so no cell is excluded on that basis. Recorded as an INDEPENDENCE note so the pair is not assumed related.</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:720-722</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. wdata/wstrb/wuser ride the same beat but cannot gate it; m_axi_wlast selects WHICH beat is last, not whether this one pops; the channel id only selects which SRAM lane is read. Burst bookkeeping (r_w_beats_remaining) reaches this cone only via r_w_active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E91" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: r_w_active &amp; sram_valid_reg &amp; sram_valid_comb &amp; wready</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      r_w_active &amp; sram_valid_reg &amp; sram_valid_comb &amp; wready</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>w_phase_fifo_pop</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:776-787</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>pop = (!r_w_active &amp;&amp; !fifo_empty) || (m_axi_wvalid &amp;&amp; m_axi_wready &amp;&amp; m_axi_wlast &amp;&amp; !fifo_empty)   [w_fire = wvalid &amp;&amp; wready]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>rows = r_w_active/fifo_empty   cols = w_fire/wlast</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s only in the fifo_empty=0 columns: start-from-idle (active=0) and burst-chain-through (w_fire &amp;&amp; wlast, no bubble between back-to-back bursts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    w_fire implies r_w_active: m_axi_wvalid IS r_w_active, so a beat cannot fire while the burst is inactive. The active=0 &amp;&amp; w_fire=1 cells are unreachable, not 0.</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:720</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E110" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B113" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: !r_w_active &amp; !fifo_empty  |  !fifo_empty &amp; w_fire &amp; wlast</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (3 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>sched_wr_error[i] latch enable</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:951</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="inlineStr">
+        <is>
+          <t>latch r_wr_error[bid] on: m_axi_bvalid &amp;&amp; m_axi_bready &amp;&amp; (m_axi_bresp != 2'b00)   [bready is constant 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = bvalid/resp_ok   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0). bready==1 always (projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:941), so bvalid alone qualifies the beat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
+      <c r="B128" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B86" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="B129" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B87" s="11" t="n">
+      <c r="B130" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: m_axi_wvalid &amp; m_axi_wready</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="inlineStr">
-        <is>
-          <t>w_phase_fifo_pop</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:776-787</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="6" t="inlineStr">
-        <is>
-          <t>pop = (!r_w_active &amp;&amp; !fifo_empty) || (m_axi_wvalid &amp;&amp; m_axi_wready &amp;&amp; m_axi_wlast &amp;&amp; !fifo_empty)   [w_fire = wvalid &amp;&amp; wready]</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>rows = r_w_active/fifo_empty   cols = w_fire/wlast</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s only in the fifo_empty=0 columns: start-from-idle (active=0) and burst-chain-through (w_fire &amp;&amp; wlast, no bubble between back-to-back bursts). Cells with active=0 &amp;&amp; w_fire=1 are unreachable (m_axi_wvalid requires r_w_active).</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C100" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D100" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E100" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C101" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D101" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B102" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B103" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B104" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C104" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: !r_w_active &amp; !fifo_empty  |  !fifo_empty &amp; w_fire &amp; wlast</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="inlineStr">
-        <is>
-          <t>sched_wr_error[i] latch enable</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:951</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>latch r_wr_error[bid] on: m_axi_bvalid &amp;&amp; m_axi_bready &amp;&amp; (m_axi_bresp != 2'b00)   [bready is constant 1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = bvalid/resp_ok   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0). bready==1 always (projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:941), so bvalid alone qualifies the beat.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B117" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B118" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B119" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B120" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: bvalid &amp; !resp_ok</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="13" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
@@ -4699,7 +5241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E243"/>
+  <dimension ref="A1:E257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4769,14 +5311,14 @@
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -4921,99 +5463,80 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: 1s ONLY on the wr_need_base=0 page, in the completing_now=0 columns, only at (state=1, rem=1, commit_zero=0). The explicit issue_rem_nz term is load-bearing: w_write_complete tracks COMMITS now, so without it the engine would keep valid high through the commit-wait with sched_wr_beats==0 and issue a garbage AW (transfer-size underflow -&gt; awlen=0xFF). NOTE commit_zero=1 with rem=1 cannot occur in practice (commits cannot complete before issue), so that half is unreachable cover, not a functional path.</t>
+          <t>CHECK BY INSPECTION: 1s ONLY on the wr_need_base=0 page, in the completing_now=0 columns, only at (state=1, rem=1, commit_zero=0). The explicit issue_rem_nz term is load-bearing: w_write_complete tracks COMMITS now, so without it the engine would keep valid high through the commit-wait with sched_wr_beats==0 and issue a garbage AW (transfer-size underflow -&gt; awlen=0xFF).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    commit_zero mirrors w_write_complete = (r_write_beats_to_commit == 0); issue_rem_nz mirrors r_write_beats_remaining != 0. These are DIFFERENT counters -- beats-to-commit vs beats-to-issue -- and commits trail issues, so 'all committed' while beats remain to issue does not occur. NOTE this is an ORDERING invariant on two counters, not a one-hot impossibility: the checker confirms it excludes cells, not that the ordering holds.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:907, :1005, :999</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>[wr_need_base=0]</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="9" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D31" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr">
+      <c r="E31" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B32" s="11" t="n">
-        <v>1</v>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="C32" s="10" t="n">
         <v>0</v>
@@ -5028,93 +5551,101 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="B35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
         <is>
           <t>[wr_need_base=1]</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="B36" s="9" t="inlineStr">
+    <row r="38">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C36" s="9" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D36" s="9" t="inlineStr">
+      <c r="D38" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E36" s="9" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
@@ -5133,2105 +5664,2298 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E40" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E41" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: state_xfer &amp; issue_rem_nz &amp; !commit_zero &amp; !completing_now &amp; !wr_need_base</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="13" t="inlineStr">
+      <c r="B42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: state_xfer &amp; issue_rem_nz &amp; !completing_now &amp; !wr_need_base</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 8 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>w_addrgen_start  (run-base generator start; EXT only)</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:317</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>w_addrgen_start = w_state_fetch_desc &amp;&amp; !r_fetch_desc_d &amp;&amp; w_is_ext</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>rows = state_fetch_desc/entry_edge   cols = is_ext</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1). The is_ext term is the TASK-059 FIX: without it a LEGACY descriptor also pulses start, running stream_run_addr_gen with its own base and STALE r_descriptor_ext strides. The generator's run-base FIFO has no flush (gaxi_fifo_sync clears only on rst_n) and legacy never consumes bases, so those bogus bases are consumed by the NEXT chained strided/transpose descriptor -&gt; reads the wrong source and writes into the previous descriptor's region (silent corruption). A contiguous EXT descriptor hides it (single-run generation emits zero bases). See known_issues/resolved/extended_chained_transpose.md.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="52">
-      <c r="B52" s="9" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C52" s="9" t="inlineStr">
+      <c r="C55" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B54" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C54" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B59" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: state_fetch_desc &amp; entry_edge &amp; is_ext</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>w_transfer_complete  (per-descriptor advance gate)</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:906</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
         <is>
           <t>w_transfer_complete = w_read_complete &amp;&amp; w_write_issued   [ISSUE-based on purpose: chained descriptors stream while their writes commit in the background]</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = read_complete/write_issued   cols = </t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1). Commit-gating this (as a past edit did) serializes the write drain at every descriptor boundary - the regression that motivated the issue/commit split.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="68">
-      <c r="B68" s="9" t="inlineStr">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B70" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+      <c r="B75" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: read_complete &amp; write_issued</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t>CH_XFER_DATA exit decision</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D80" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:523-527</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>if (w_wr_advance) stay-XFER (in-place descriptor advance) ; else if (w_transfer_complete &amp;&amp; !r_rd_ahead) -&gt; CH_COMPLETE ; else hold</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>rows = wr_advance/transfer_complete   cols = rd_ahead</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: advance fills the whole wr_advance=1 half (priority). COMPLETE only at (0,1,0): while read runs ahead (rd_ahead=1) the completion exit is SUPPRESSED because w_transfer_complete keys off the READ counter which already refers to descriptor N+1.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="84">
-      <c r="B84" s="9" t="inlineStr">
+      <c r="A84" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C87" s="9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B86" s="11" t="inlineStr">
-        <is>
-          <t>COMPLETE</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="inlineStr">
-        <is>
-          <t>advance</t>
-        </is>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>advance</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B88" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>COMPLETE</t>
+        </is>
+      </c>
+      <c r="C89" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>advance</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B88" s="11" t="inlineStr">
+      <c r="B91" s="11" t="inlineStr">
         <is>
           <t>advance</t>
         </is>
       </c>
-      <c r="C88" s="11" t="inlineStr">
+      <c r="C91" s="11" t="inlineStr">
         <is>
           <t>advance</t>
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="1" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
         <is>
           <t>CH_COMPLETE exit decision</t>
         </is>
       </c>
-      <c r="D91" s="5" t="inlineStr">
+      <c r="D94" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:540-544</t>
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="6" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="6" t="inlineStr">
         <is>
           <t>if (next_ptr != 0 &amp;&amp; !last) -&gt; CH_NEXT_DESC (advance NOW, issue-based) ; else if (w_write_complete) -&gt; CH_IDLE ; else hold</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = chained/write_complete   cols = </t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="7" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: chained=1 half advances immediately regardless of commits (streaming). IDLE only at (0,1): the LAST descriptor holds here until every write has COMMITTED - the channel is never reported done while data still drains.</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="98">
-      <c r="B98" s="9" t="inlineStr">
+      <c r="A98" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="9" t="inlineStr">
         <is>
           <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B99" s="10" t="inlineStr">
-        <is>
-          <t>hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B100" s="10" t="inlineStr">
-        <is>
-          <t>IDLE</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B101" s="11" t="inlineStr">
-        <is>
-          <t>NEXT_DESC</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>IDLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>NEXT_DESC</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B102" s="11" t="inlineStr">
+      <c r="B105" s="11" t="inlineStr">
         <is>
           <t>NEXT_DESC</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="1" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
         <is>
           <t>w_rd_peek  (read-ahead loads next descriptor)</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
+      <c r="D108" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:929-931</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>w_rd_peek = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; !r_rd_ahead &amp;&amp; (r_read_beats_remaining==0) &amp;&amp; !w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid   [head_ok = w_desc_chained &amp;&amp; descriptor_valid]</t>
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+    <row r="110">
+      <c r="A110" t="inlineStr">
         <is>
           <t>rows = prefetch_en/state_xfer   cols = rd_ahead/rd_done   pages = write_issued/head_ok</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="7" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the [write_issued=0, head_ok=1] page, single cell (prefetch_en=1, state_xfer=1, rd_ahead=0, rd_done=1). rd_ahead=0 caps read-ahead at ONE descriptor; write_issued=0 means the write side still owns the FIFO head, so peek must NOT pop it.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="112">
-      <c r="A112" s="8" t="inlineStr">
+      <c r="A112" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>[write_issued=0, head_ok=0]</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="B113" s="9" t="inlineStr">
+    <row r="116">
+      <c r="B116" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C113" s="9" t="inlineStr">
+      <c r="C116" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D113" s="9" t="inlineStr">
+      <c r="D116" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E113" s="9" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B114" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B115" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B116" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B117" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="8" t="inlineStr">
+      <c r="B120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
         <is>
           <t>[write_issued=0, head_ok=1]</t>
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="B120" s="9" t="inlineStr">
+    <row r="123">
+      <c r="B123" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C120" s="9" t="inlineStr">
+      <c r="C123" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D120" s="9" t="inlineStr">
+      <c r="D123" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E120" s="9" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B123" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B124" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="8" t="inlineStr">
+      <c r="B127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
         <is>
           <t>[write_issued=1, head_ok=0]</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="B127" s="9" t="inlineStr">
+    <row r="130">
+      <c r="B130" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C127" s="9" t="inlineStr">
+      <c r="C130" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D127" s="9" t="inlineStr">
+      <c r="D130" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E127" s="9" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B129" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B130" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B133" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C133" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="8" t="inlineStr">
+      <c r="B134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
         <is>
           <t>[write_issued=1, head_ok=1]</t>
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="B134" s="9" t="inlineStr">
+    <row r="137">
+      <c r="B137" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C134" s="9" t="inlineStr">
+      <c r="C137" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D134" s="9" t="inlineStr">
+      <c r="D137" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E134" s="9" t="inlineStr">
+      <c r="E137" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B136" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C136" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B138" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C138" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="inlineStr">
+      <c r="B141" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C141" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D141" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: prefetch_en &amp; state_xfer &amp; !rd_ahead &amp; rd_done &amp; !write_issued &amp; head_ok</t>
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="13" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="1" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
         <is>
           <t>w_wr_advance  (in-place descriptor advance + FIFO pop)</t>
         </is>
       </c>
-      <c r="D143" s="5" t="inlineStr">
+      <c r="D146" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:939-940</t>
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="6" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
         <is>
           <t>w_wr_advance = w_rd_prefetch_en &amp;&amp; w_state_xfer_data &amp;&amp; w_write_issued &amp;&amp; w_desc_chained &amp;&amp; descriptor_valid</t>
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
+    <row r="148">
+      <c r="A148" t="inlineStr">
         <is>
           <t>rows = prefetch_en/state_xfer   cols = write_issued/chained   pages = desc_valid</t>
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="7" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the [desc_valid=1] page, single cell at all-ones. This is the ONLY XFER-state descriptor_ready source: it pops the FIFO head that peek borrowed. prefetch_en=0 forces the whole map to 0 (lockstep A/B on one bitstream).</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
     <row r="150">
-      <c r="A150" s="8" t="inlineStr">
+      <c r="A150" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>[desc_valid=0]</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="B151" s="9" t="inlineStr">
+    <row r="154">
+      <c r="B154" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C151" s="9" t="inlineStr">
+      <c r="C154" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D151" s="9" t="inlineStr">
+      <c r="D154" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E151" s="9" t="inlineStr">
+      <c r="E154" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B152" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C152" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D152" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D153" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E153" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B154" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C154" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D154" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D155" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D156" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E157" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B155" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C155" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D155" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="8" t="inlineStr">
+      <c r="B158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="8" t="inlineStr">
         <is>
           <t>[desc_valid=1]</t>
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="B158" s="9" t="inlineStr">
+    <row r="161">
+      <c r="B161" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C158" s="9" t="inlineStr">
+      <c r="C161" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D158" s="9" t="inlineStr">
+      <c r="D161" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E158" s="9" t="inlineStr">
+      <c r="E161" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B159" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C159" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D159" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B160" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C160" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D160" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E160" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B161" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C161" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D161" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B163" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C163" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D163" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B162" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C162" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D162" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="6" t="inlineStr">
+      <c r="B165" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C165" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D165" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: prefetch_en &amp; state_xfer &amp; write_issued &amp; chained &amp; desc_valid</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="13" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
         <is>
           <t>descriptor_ready  (FIFO pop)</t>
         </is>
       </c>
-      <c r="D167" s="5" t="inlineStr">
+      <c r="D170" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1077-1079</t>
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="6" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>descriptor_ready = (state==CH_IDLE) || (state==CH_NEXT_DESC) || w_wr_advance</t>
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
+    <row r="172">
+      <c r="A172" t="inlineStr">
         <is>
           <t>rows = state_idle/state_next_desc   cols = wr_advance</t>
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros. idle/next_desc are mutually exclusive (one-hot FSM) and wr_advance can only be 1 in CH_XFER_DATA, so at most one source is live per cycle - the (1,1,x) cells are unreachable cover.</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+    <row r="173">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: OR of three sources; zero only at all-zeros.</t>
         </is>
       </c>
     </row>
     <row r="174">
-      <c r="B174" s="9" t="inlineStr">
+      <c r="A174" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    state_idle and state_next_desc are equality tests on the SAME one-hot channel_state_t register, so they cannot both be 1.</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:228, :232</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    wr_advance is live only in CH_XFER_DATA, which is neither CH_IDLE nor CH_NEXT_DESC -- so it cannot coincide with either.</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:230, :1080</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C174" s="9" t="inlineStr">
+      <c r="C180" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="9" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B175" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C175" s="11" t="n">
+      <c r="B181" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C181" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="9" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B176" s="11" t="n">
+      <c r="B182" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C176" s="11" t="n">
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B183" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C183" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B184" s="11" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B177" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C177" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B178" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="6" t="inlineStr">
+      <c r="C184" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: wr_advance  |  state_next_desc  |  state_idle</t>
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
-        </is>
-      </c>
-      <c r="D183" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1170-1171</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="6" t="inlineStr">
-        <is>
-          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). A bare timeout window is deliberately NOT in this cone - it escalates separately via w_timeout_escalate (strikes &gt;= cfg_sched_timeout_limit).</t>
-        </is>
-      </c>
-    </row>
     <row r="187">
-      <c r="A187" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+      <c r="A187" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (3 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
     <row r="190">
-      <c r="B190" s="9" t="inlineStr">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t>w_hard_error  (fatal -&gt; sticky CH_ERROR)</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1170-1171</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="6" t="inlineStr">
+        <is>
+          <t>w_hard_error = descriptor_error || sched_rd_error || sched_wr_error || r_read_error_sticky || r_write_error_sticky   [rd_any = live|sticky, wr_any = live|sticky]</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>rows = descriptor_error/rd_any   cols = wr_any</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Zero ONLY at all-zeros (pure OR). THE WORD 'TIMEOUT' IS OVERLOADED HERE AND THAT IS THE HAZARD: this is the SCHEDULER timeout (cfg_sched_timeout_cycles), NOT the monitor timeout. A bare scheduler timeout window is recoverable and deliberately NOT latched into this cone -- only an ESCALATED one is, after cfg_sched_timeout_limit consecutive windows (projects/components/dmas/stream/rtl/fub/scheduler.sv:1144-1147). Two mechanisms sharing a word is how the monitor's timeout went untested at this level for so long.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D195" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="5" t="inlineStr">
+        <is>
+          <t>descriptor_error</t>
+        </is>
+      </c>
+      <c r="B196" s="6" t="inlineStr">
+        <is>
+          <t>r_descriptor_error -- latched fatal fault OR escalated timeout</t>
+        </is>
+      </c>
+      <c r="D196" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1147</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="5" t="inlineStr">
+        <is>
+          <t>rd_any</t>
+        </is>
+      </c>
+      <c r="B197" s="6" t="inlineStr">
+        <is>
+          <t>sched_rd_error | r_read_error_sticky  (live OR sticky)</t>
+        </is>
+      </c>
+      <c r="D197" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1141</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="5" t="inlineStr">
+        <is>
+          <t>wr_any</t>
+        </is>
+      </c>
+      <c r="B198" s="6" t="inlineStr">
+        <is>
+          <t>sched_wr_error | r_write_error_sticky (live OR sticky)</t>
+        </is>
+      </c>
+      <c r="D198" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1142</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) Every axis is sticky-or-live: once set, a sticky holds until channel reset, so all eight combinations are reachable and NOTHING is excluded. Stated explicitly -- an OR cone with no unreachable cells is a real result, not a missing argument.</t>
+        </is>
+      </c>
+      <c r="D200" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1141-1142, :1154-1156</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. The timeout counter reaches this cone ONLY via w_timeout_escalate folded into descriptor_error; the counter itself re-arms per window and never latches (projects/components/dmas/stream/rtl/fub/scheduler.sv:1120-1121). Channel reset is a CLEAR, not an input to the OR: it zeroes all three stickies together (projects/components/dmas/stream/rtl/fub/scheduler.sv:1154-1156), which is why no clear term appears as an axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C190" s="9" t="inlineStr">
+      <c r="C203" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="191">
-      <c r="A191" s="9" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B191" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C191" s="11" t="n">
+      <c r="B204" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C204" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="9" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B192" s="11" t="n">
+      <c r="B205" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C192" s="11" t="n">
+      <c r="C205" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="193">
-      <c r="A193" s="9" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B193" s="11" t="n">
+      <c r="B206" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C193" s="11" t="n">
+      <c r="C206" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="194">
-      <c r="A194" s="9" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B194" s="11" t="n">
+      <c r="B207" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C194" s="11" t="n">
+      <c r="C207" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="196">
-      <c r="A196" s="6" t="inlineStr">
+    <row r="209">
+      <c r="A209" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: wr_any  |  rd_any  |  descriptor_error</t>
         </is>
       </c>
     </row>
-    <row r="197">
-      <c r="A197" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr">
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      descriptor_error | rd_any | wr_any</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="inlineStr">
         <is>
           <t>r_timeout_counter next-value (priority order)</t>
         </is>
       </c>
-      <c r="D199" s="5" t="inlineStr">
+      <c r="D213" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1118-1126</t>
         </is>
       </c>
     </row>
-    <row r="200">
-      <c r="A200" s="7" t="inlineStr">
+    <row r="214">
+      <c r="A214" s="7" t="inlineStr">
         <is>
           <t>w_timeout_expired = cfg_sched_timeout_enable &amp;&amp; (counter &gt;= cfg_sched_timeout_cycles) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1147-1148). Escalation: w_timeout_escalate = (limit != 0) &amp;&amp; (strikes &gt;= limit) (projects/components/dmas/stream/rtl/fub/scheduler.sv:1152-1153); strikes clear on any progress or CH_IDLE.</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="3" t="inlineStr">
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
         <is>
           <t>condition (first match wins)</t>
         </is>
       </c>
-      <c r="B201" s="3" t="inlineStr">
+      <c r="B215" s="3" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="C201" s="3" t="inlineStr">
+      <c r="C215" s="3" t="inlineStr">
         <is>
           <t>meaning</t>
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="4" t="inlineStr">
+    <row r="216">
+      <c r="A216" s="4" t="inlineStr">
         <is>
           <t>sched_wr_done_strobe || sched_wr_commit_strobe</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
+      <c r="B216" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr">
+      <c r="C216" s="4" t="inlineStr">
         <is>
           <t>ANY write progress (AW issue OR B commit) re-arms - commits count as progress because completion is commit-gated</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+    <row r="217">
+      <c r="A217" s="4" t="inlineStr">
         <is>
           <t>w_timeout_expired</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B217" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="C217" s="4" t="inlineStr">
         <is>
           <t>window elapsed -&gt; re-arm and keep waiting (SOFT timeout, one pulse per window)</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
         <is>
           <t>sched_wr_valid &amp;&amp; !sched_wr_ready</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B218" s="4" t="inlineStr">
         <is>
           <t>counter + 1</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
+      <c r="C218" s="4" t="inlineStr">
         <is>
           <t>genuinely waiting on the write engine</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="4" t="inlineStr">
-        <is>
-          <t>otherwise</t>
-        </is>
-      </c>
-      <c r="B205" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C205" s="4" t="inlineStr">
-        <is>
-          <t>not waiting</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr">
-        <is>
-          <t>FSM transition priority</t>
-        </is>
-      </c>
-      <c r="D208" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:464-478</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" s="7" t="inlineStr">
-        <is>
-          <t>CH_ERROR self-loops until channel reset; scheduler_idle reports CH_IDLE only (a wedged channel must NOT read idle).</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B210" s="3" t="inlineStr">
-        <is>
-          <t>condition</t>
-        </is>
-      </c>
-      <c r="C210" s="3" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B211" s="4" t="inlineStr">
-        <is>
-          <t>r_channel_reset_active</t>
-        </is>
-      </c>
-      <c r="C211" s="4" t="inlineStr">
-        <is>
-          <t>-&gt; CH_IDLE (overrides all)</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B212" s="4" t="inlineStr">
-        <is>
-          <t>w_hard_error || w_timeout_escalate</t>
-        </is>
-      </c>
-      <c r="C212" s="4" t="inlineStr">
-        <is>
-          <t>-&gt; CH_ERROR (sticky)</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B213" s="4" t="inlineStr">
-        <is>
-          <t>state case (normal transitions)</t>
-        </is>
-      </c>
-      <c r="C213" s="4" t="inlineStr">
-        <is>
-          <t>see exit-decision maps</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" s="1" t="inlineStr">
-        <is>
-          <t>run-base generator: TERMS</t>
-        </is>
-      </c>
-      <c r="D216" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1021-1062, projects/components/misc/rtl/stream_run_addr_gen.sv:152-221</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" s="7" t="inlineStr">
-        <is>
-          <t>u_rd_addr_gen / u_wr_addr_gen are instantiated per direction; the block is shared with RAPIDS, so an RTL change has two consumers.</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="3" t="inlineStr">
-        <is>
-          <t>term</t>
-        </is>
-      </c>
-      <c r="B218" s="3" t="inlineStr">
-        <is>
-          <t>defining expression</t>
-        </is>
-      </c>
-      <c r="C218" s="3" t="inlineStr">
-        <is>
-          <t>source</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="inlineStr">
         <is>
+          <t>otherwise</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>not waiting</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>FSM transition priority</t>
+        </is>
+      </c>
+      <c r="D222" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:464-478</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="7" t="inlineStr">
+        <is>
+          <t>CH_ERROR self-loops until channel reset; scheduler_idle reports CH_IDLE only (a wedged channel must NOT read idle).</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B224" s="3" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="C224" s="3" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>r_channel_reset_active</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; CH_IDLE (overrides all)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>w_hard_error || w_timeout_escalate</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>-&gt; CH_ERROR (sticky)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>state case (normal transitions)</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>see exit-decision maps</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>run-base generator: TERMS</t>
+        </is>
+      </c>
+      <c r="D230" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1021-1062, projects/components/misc/rtl/stream_run_addr_gen.sv:152-221</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="7" t="inlineStr">
+        <is>
+          <t>u_rd_addr_gen / u_wr_addr_gen are instantiated per direction; the block is shared with RAPIDS, so an RTL change has two consumers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>term</t>
+        </is>
+      </c>
+      <c r="B232" s="3" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="C232" s="3" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="inlineStr">
+        <is>
           <t>chan_reset</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B233" s="4" t="inlineStr">
         <is>
           <t>r_channel_reset_active (registered cfg_channel_reset)</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr">
+      <c r="C233" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:440</t>
         </is>
       </c>
     </row>
-    <row r="220">
-      <c r="A220" s="4" t="inlineStr">
+    <row r="234">
+      <c r="A234" s="4" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
+      <c r="B234" s="4" t="inlineStr">
         <is>
           <t>w_addrgen_start -&gt; stream_run_addr_gen.start</t>
         </is>
       </c>
-      <c r="C220" s="4" t="inlineStr">
+      <c r="C234" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1030</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="4" t="inlineStr">
+    <row r="235">
+      <c r="A235" s="4" t="inlineStr">
         <is>
           <t>fifo_nonempty</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
+      <c r="B235" s="4" t="inlineStr">
         <is>
           <t>o_base_valid (i_addr_fifo rd_valid)</t>
         </is>
       </c>
-      <c r="C221" s="4" t="inlineStr">
+      <c r="C235" s="4" t="inlineStr">
         <is>
           <t>projects/components/misc/rtl/stream_run_addr_gen.sv:217</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+    <row r="236">
+      <c r="A236" s="4" t="inlineStr">
         <is>
           <t>gen_rst</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B236" s="4" t="inlineStr">
         <is>
           <t>i_addr_fifo.axi_aresetn == rst_n (BLOCK reset)</t>
         </is>
       </c>
-      <c r="C222" s="4" t="inlineStr">
+      <c r="C236" s="4" t="inlineStr">
         <is>
           <t>projects/components/misc/rtl/stream_run_addr_gen.sv:213</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="1" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="1" t="inlineStr">
         <is>
           <t>run-base generator: INVARIANTS</t>
         </is>
       </c>
-      <c r="D225" s="5" t="inlineStr">
+      <c r="D239" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1029, projects/components/misc/rtl/stream_run_addr_gen.sv:152</t>
         </is>
       </c>
     </row>
-    <row r="226">
-      <c r="A226" s="7" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="7" t="inlineStr">
         <is>
           <t>I1 and I2 do not EXCLUDE the hazard rows below -- they produce them. That is the finding, not a footnote.</t>
         </is>
       </c>
     </row>
-    <row r="227">
-      <c r="A227" s="3" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B227" s="3" t="inlineStr">
+      <c r="B241" s="3" t="inlineStr">
         <is>
           <t>invariant</t>
         </is>
       </c>
-      <c r="C227" s="3" t="inlineStr">
+      <c r="C241" s="3" t="inlineStr">
         <is>
           <t>citation</t>
         </is>
       </c>
-      <c r="D227" s="3" t="inlineStr">
+      <c r="D241" s="3" t="inlineStr">
         <is>
           <t>consequence for the table</t>
         </is>
       </c>
     </row>
-    <row r="228">
-      <c r="A228" s="4" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="4" t="inlineStr">
         <is>
           <t>I1</t>
         </is>
       </c>
-      <c r="B228" s="4" t="inlineStr">
+      <c r="B242" s="4" t="inlineStr">
         <is>
           <t>channel reset NEVER reaches the generator: .rst_n is wired to the block reset, not r_channel_reset_active</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr">
+      <c r="C242" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1029, :1051</t>
         </is>
       </c>
-      <c r="D228" s="4" t="inlineStr">
+      <c r="D242" s="4" t="inlineStr">
         <is>
           <t>chan_reset cannot empty i_addr_fifo</t>
         </is>
       </c>
     </row>
-    <row r="229">
-      <c r="A229" s="4" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="4" t="inlineStr">
         <is>
           <t>I2</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
+      <c r="B243" s="4" t="inlineStr">
         <is>
           <t>start re-arms the WALKER only (r_inner_count, r_gen_beats, indices); it does not clear i_addr_fifo</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr">
+      <c r="C243" s="4" t="inlineStr">
         <is>
           <t>projects/components/misc/rtl/stream_run_addr_gen.sv:152</t>
         </is>
       </c>
-      <c r="D229" s="4" t="inlineStr">
+      <c r="D243" s="4" t="inlineStr">
         <is>
           <t>a new descriptor generates BEHIND whatever is still queued</t>
         </is>
       </c>
     </row>
-    <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="4" t="inlineStr">
         <is>
           <t>I3</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B244" s="4" t="inlineStr">
         <is>
           <t>i_addr_fifo depth is 4 per direction</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr">
+      <c r="C244" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1025, projects/components/misc/rtl/stream_run_addr_gen.sv:210</t>
         </is>
       </c>
-      <c r="D230" s="4" t="inlineStr">
+      <c r="D244" s="4" t="inlineStr">
         <is>
           <t>bounds the stale-base exposure at 4 addresses per direction</t>
         </is>
       </c>
     </row>
-    <row r="233">
-      <c r="A233" s="1" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
         <is>
           <t>run-base generator: DECISION TABLE (FIFO content at next start)</t>
         </is>
       </c>
-      <c r="D233" s="5" t="inlineStr">
+      <c r="D247" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/scheduler.sv:1021-1062, projects/components/misc/rtl/stream_run_addr_gen.sv:152-221</t>
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="7" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="7" t="inlineStr">
         <is>
           <t>NO row is ILLEGAL: every combination is reachable, so nothing structurally prevents the stale-base case -- it is bounded (4 per direction), not excluded. Severity is low because w_addrgen_start only pulses for EXT descriptors (projects/components/dmas/stream/rtl/fub/scheduler.sv:1030) and channel reset mid-generation is rare. A gaxi_drop_fifo_sync drop_all flush-on-start was attempted and reverted after it regressed working cases on a flush/read timing interaction; that attempt was never committed, so it cannot be inspected. Note gaxi_drop_fifo_sync blocks normal read/write for the duration of a drop, which is the likely mechanism. Documented rather than fixed: see STREAM TASK-058.</t>
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="3" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
         <is>
           <t>chan_reset</t>
         </is>
       </c>
-      <c r="B235" s="3" t="inlineStr">
+      <c r="B249" s="3" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="C235" s="3" t="inlineStr">
+      <c r="C249" s="3" t="inlineStr">
         <is>
           <t>fifo_nonempty</t>
         </is>
       </c>
-      <c r="D235" s="3" t="inlineStr">
+      <c r="D249" s="3" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
       </c>
-      <c r="E235" s="3" t="inlineStr">
+      <c r="E249" s="3" t="inlineStr">
         <is>
           <t>behaviour / excluded by</t>
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C236" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D236" s="4" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C250" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
+      <c r="E250" s="4" t="inlineStr">
         <is>
           <t>idle, nothing queued</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B237" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C237" s="4" t="n">
+    <row r="251">
+      <c r="A251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B251" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C251" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D237" s="4" t="inlineStr">
+      <c r="D251" s="4" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E237" s="4" t="inlineStr">
+      <c r="E251" s="4" t="inlineStr">
         <is>
           <t>normal drain: consumer pops generated bases</t>
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B238" s="4" t="n">
+    <row r="252">
+      <c r="A252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B252" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C238" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="C252" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
+      <c r="E252" s="4" t="inlineStr">
         <is>
           <t>intended case - start on an empty FIFO</t>
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="B239" s="4" t="n">
+    <row r="253">
+      <c r="A253" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="B253" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C239" s="4" t="n">
+      <c r="C253" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D253" s="4" t="inlineStr">
         <is>
           <t>legal (benign)</t>
         </is>
       </c>
-      <c r="E239" s="4" t="inlineStr">
+      <c r="E253" s="4" t="inlineStr">
         <is>
           <t>start while this descriptor's own bases are still queued; the walker reloads and appends in order</t>
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="4" t="n">
+    <row r="254">
+      <c r="A254" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B240" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C240" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D240" s="4" t="inlineStr">
+      <c r="B254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C254" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
+      <c r="E254" s="4" t="inlineStr">
         <is>
           <t>channel reset with an already-empty FIFO</t>
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="4" t="n">
+    <row r="255">
+      <c r="A255" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B241" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C241" s="4" t="n">
+      <c r="B255" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C255" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D255" s="4" t="inlineStr">
         <is>
           <t>HAZARD</t>
         </is>
       </c>
-      <c r="E241" s="4" t="inlineStr">
+      <c r="E255" s="4" t="inlineStr">
         <is>
           <t>reset returns the FSM to CH_IDLE but leaves up to 4 stale bases per direction (I1, I2, I3)</t>
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="4" t="n">
+    <row r="256">
+      <c r="A256" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B242" s="4" t="n">
+      <c r="B256" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C242" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D242" s="4" t="inlineStr">
+      <c r="C256" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D256" s="4" t="inlineStr">
         <is>
           <t>legal</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
+      <c r="E256" s="4" t="inlineStr">
         <is>
           <t>reset then restart with an empty FIFO</t>
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="4" t="n">
+    <row r="257">
+      <c r="A257" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B243" s="4" t="n">
+      <c r="B257" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C243" s="4" t="n">
+      <c r="C257" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D243" s="4" t="inlineStr">
+      <c r="D257" s="4" t="inlineStr">
         <is>
           <t>HAZARD</t>
         </is>
       </c>
-      <c r="E243" s="4" t="inlineStr">
+      <c r="E257" s="4" t="inlineStr">
         <is>
           <t>next descriptor generates behind stale bases; the consumer pops the STALE ones first (I1, I2, I3)</t>
         </is>
@@ -7248,7 +7972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -7311,14 +8035,14 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -7436,14 +8160,14 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -7554,625 +8278,605 @@
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. eligible &amp;&amp; committed &amp;&amp; !push (throttled or FIFO full) does NOT lose the fetch - it arms r_chain_pending (deferred path below).</t>
+          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. eligible &amp;&amp; committed &amp;&amp; !push (throttled or FIFO full) does NOT lose the fetch - it arms r_chain_pending (deferred path below). BUG FIX: cfg_prefetch_enable and cfg_fifo_threshold were previously DEAD -- wired nowhere. They reach this cone ONLY through prefetch_allows, via w_prefetch_limit's three-arm mux: disabled -&gt; 1 (on-demand), threshold==0 -&gt; 1 (guard, since 0 would stall chaining outright), else the threshold (projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:469-474). An axis list carrying defining expressions is what shows an axis that no RTL drives.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>eligible</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>w_chain_eligible = w_chain_condition &amp;&amp; &lt;window/enable terms&gt;</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:457</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="9" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>committed</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>w_desc_committed = (r_current_state == RD_COMPLETE) &amp;&amp; w_desc_fifo_wr_ready  -- COMPOSITE, see the invariant below</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:462</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>prefetch_allows</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>w_prefetch_allows = (w_desc_fifo_count &lt; w_prefetch_limit)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:476</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>addr_fifo_ready</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>w_desc_addr_fifo_wr_ready -- address FIFO has room</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:479</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) committed is COMPOSITE: (state==RD_COMPLETE) &amp;&amp; w_desc_fifo_wr_ready. Kept as one axis because both conjuncts must hold to commit and neither can be observed separately at this cone -- the collapse is recorded here rather than hidden, per criterion 3.</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:462</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) prefetch_allows already folds cfg_prefetch_enable and cfg_fifo_threshold through w_prefetch_limit; the guard arm means limit is never 0, so prefetch_allows cannot be permanently false from a zero threshold.</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:469-476</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. The descriptor payload (address, length, flags) decides WHAT is fetched, never whether the chain pushes. The deferred path (r_chain_pending) is downstream of this signal, not upstream. cfg_prefetch_enable / cfg_fifo_threshold are NOT separate axes on purpose: they enter only via prefetch_allows, and collapsing them there is licensed by the invariant below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D51" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E43" s="9" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="9" t="inlineStr">
+      <c r="B52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+      <c r="B53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="11" t="n">
+      <c r="B54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+      <c r="E54" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
+      <c r="B55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: eligible &amp; committed &amp; prefetch_allows &amp; addr_fifo_ready</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      eligible &amp; committed &amp; prefetch_allows &amp; addr_fifo_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>w_pending_push_fire  (deferred chain push)</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:485-486</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
         <is>
           <t>w_pending_push_fire = r_chain_pending &amp;&amp; w_prefetch_allows &amp;&amp; w_desc_addr_fifo_wr_ready &amp;&amp; !w_desc_committed</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>rows = chain_pending/prefetch_allows   cols = addr_fifo_ready/committed</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,1,1,0). The !committed term keeps the commit cycle reserved for the immediate path - both pushing in one cycle would double-write the address FIFO mux.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D59" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E59" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B60" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="11" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="65">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: chain_pending &amp; prefetch_allows &amp; addr_fifo_ready &amp; !committed</t>
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: chain_pending &amp; prefetch_allows &amp; addr_fifo_ready &amp; !committed</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
         <is>
           <t>w_prefetch_limit  (chain throttle)</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D77" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:468-476</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="7" t="inlineStr">
         <is>
           <t>w_prefetch_allows = (w_desc_fifo_count &lt; w_prefetch_limit) (projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:476). BUG FIX: cfg_prefetch_enable / cfg_fifo_threshold were previously DEAD (unwired) - wiring them into this throttle was half of the top-level multi_channel/stress hang fix.</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>cfg_prefetch_enable</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
         <is>
           <t>cfg_fifo_threshold</t>
         </is>
       </c>
-      <c r="C70" s="3" t="inlineStr">
+      <c r="C79" s="3" t="inlineStr">
         <is>
           <t>limit</t>
         </is>
       </c>
-      <c r="D70" s="3" t="inlineStr">
+      <c r="D79" s="3" t="inlineStr">
         <is>
           <t>behavior</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B80" s="4" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C80" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D71" s="4" t="inlineStr">
+      <c r="D80" s="4" t="inlineStr">
         <is>
           <t>on-demand: fetch next only after the scheduler drains the current descriptor</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B81" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C81" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D81" s="4" t="inlineStr">
         <is>
           <t>guard: threshold 0 would stall chaining forever</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
+      <c r="B82" s="4" t="inlineStr">
         <is>
           <t>N&gt;0</t>
         </is>
       </c>
-      <c r="C73" s="4" t="inlineStr">
+      <c r="C82" s="4" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D82" s="4" t="inlineStr">
         <is>
           <t>buffer up to N fetched-but-unconsumed descriptors ahead of the scheduler</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
         <is>
           <t>APB accept  (w_apb_skid_valid_in / apb_ready)</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D85" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:333-336</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="6" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>accept = apb_valid &amp;&amp; !r_channel_reset_active &amp;&amp; w_desc_addr_fifo_empty &amp;&amp; channel_idle &amp;&amp; !r_apb_ip   [apb_ready has the same gate off the skid ready]</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>rows = apb_valid/reset_active   cols = addr_fifo_empty/channel_idle   pages = apb_ip</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: 1s ONLY on the apb_ip=0 page, in the channel_idle=1 columns, single cell (valid=1, reset=0, fifo_empty=1). fifo_empty prevents APB from clobbering a queued chain address; apb_ip prevents accepting a second kick before the first chain completes (cleared on the channel_idle falling edge).</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>[apb_ip=0]</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="B84" s="9" t="inlineStr">
+    <row r="93">
+      <c r="B93" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="C84" s="9" t="inlineStr">
+      <c r="C93" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D93" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E93" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B86" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B88" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="8" t="inlineStr">
-        <is>
-          <t>[apb_ip=1]</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E91" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="B94" s="10" t="n">
@@ -8191,264 +8895,437 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B95" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C95" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="6" t="inlineStr">
+      <c r="B97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>[apb_ip=1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E100" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: apb_valid &amp; !reset_active &amp; addr_fifo_empty &amp; channel_idle &amp; !apb_ip</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="13" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="1" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
         <is>
           <t>ar_valid  (descriptor fetch AR)</t>
         </is>
       </c>
-      <c r="D100" s="5" t="inlineStr">
+      <c r="D109" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:920-921</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="6" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
         <is>
           <t>ar_valid = ((state==RD_ISSUE_ADDR) || (state==RD_ISSUE_ADDR2)) &amp;&amp; !r_axi_read_active</t>
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+    <row r="111">
+      <c r="A111" t="inlineStr">
         <is>
           <t>rows = st_issue_addr/st_issue_addr2   cols = read_active</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: 1s only in the read_active=0 half. The (1,1,x) cells are unreachable (one-hot FSM). read_active latches on ar_ready and clears on the R response, so a state re-entry cannot double-issue the same AR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="B107" s="9" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: 1s only in the read_active=0 half. read_active latches on ar_ready and clears on the R response, so a state re-entry cannot double-issue the same AR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    RD_ISSUE_ADDR and RD_ISSUE_ADDR2 are distinct arms of one case on the same state register, so both cannot hold at once.</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:726, :753</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C107" s="9" t="inlineStr">
+      <c r="C118" s="9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="9" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B108" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C108" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="9" t="inlineStr">
+      <c r="B119" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C119" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B109" s="11" t="n">
+      <c r="B120" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C109" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+      <c r="C120" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B110" s="11" t="n">
+      <c r="B121" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C121" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C110" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C111" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr">
+      <c r="C122" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: st_issue_addr2 &amp; !read_active  |  st_issue_addr &amp; !read_active</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="13" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (2 ones, 2 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="1" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
         <is>
           <t>descriptor_valid  (to scheduler)</t>
         </is>
       </c>
-      <c r="D116" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/descriptor_engine.sv:1037</t>
         </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>descriptor_valid = w_desc_fifo_rd_valid &amp;&amp; !r_descriptor_error</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = fifo_rd_valid/descriptor_error   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,0): a latched fetch error blocks ALL buffered descriptors from reaching the scheduler until the error clears (RD_IDLE re-entry / channel reset).</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="B123" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B124" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B125" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B126" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B127" s="11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
+          <t>descriptor_valid = w_desc_fifo_rd_valid &amp;&amp; !r_descriptor_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = fifo_rd_valid/descriptor_error   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,0): a latched fetch error blocks ALL buffered descriptors from reaching the scheduler until the error clears (RD_IDLE re-entry / channel reset).</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B136" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B138" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B139" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
           <t>DERIVED MINIMAL SOP: fifo_rd_valid &amp; !descriptor_error</t>
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="13" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
@@ -8465,7 +9342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8528,14 +9405,14 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -8636,14 +9513,14 @@
     <row r="24">
       <c r="A24" s="13" t="inlineStr">
         <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
         </is>
       </c>
     </row>
@@ -8711,385 +9588,604 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>space_free accounting chain (read side)</t>
+          <t>over-drain reachability  (drain reserve vs occupancy)</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/fub/stream_alloc_ctrl.sv:141, projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:310-316, projects/components/dmas/stream/rtl/fub/sram_controller.sv:257-267</t>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:111, :145, :176</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>The 2-flop stage is the 100 MHz timing closure for the 8-channel arbitration cone; false-pathing it was rejected because a stale grant handshake could latch the wrong channel.</t>
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>rd_ptr advances by the FULL rd_size gated only on !rd_empty: w_rd_ptr_bin_next = r_rd_ptr_bin + (w_read &amp;&amp; !r_rd_empty ? rd_size : 0); data_available = w_count</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>stage</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>expression / register</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>staleness</t>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>rows = rd_valid/not_empty   cols = size_gt_avail</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>alloc_ctrl</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>space_free = DEPTH - (wr_ptr - rd_ptr)</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>combinational</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: The 1-cell at all-ones is the CORRUPTING case, and it is REACHABLE -- that is the finding. rd_ptr overshoots wr_ptr, the wrap-corrected occupancy computes as ~DEPTH instead of a small number, both pointers then advance in lockstep and the channel reports a nearly-full FIFO forever, stalling the shared in-order W-phase FIFO and freezing every channel (projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:156-162).</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>sram_controller_unit</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>registered once</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>1 cycle</t>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>AXES</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>sram_controller wrapper</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>registered again (axi_rd_alloc_space_free port)</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>2 cycles total</t>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>cite</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>axi_read_engine</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>w_space_ok compares the stale view</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>safe: reservations only SHRINK the stale view</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>rd_valid</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>drain request presented this cycle</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:176</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>not_empty</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>!r_rd_empty -- the only structural gate on the pointer advance</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:111</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>size_gt_avail</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>(AW+1)'(rd_size) &gt; data_available  -- the over-reservation</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:176</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>drain occupancy advance  (wr_ptr += 1)</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:184</t>
+      <c r="A45" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>.wr_valid(axi_rd_sram_valid &amp;&amp; axi_rd_sram_ready)   [data beat lands in the channel FIFO -&gt; data_available += 1]</t>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) NOTHING here is structurally unreachable. TASK-001 expected don't-cares resting on 'ordering guarantees elsewhere'; the RTL does not provide one. The only protection is a CALLER CONTRACT -- the write engine's w_effective_avail stale-view correction (projects/components/dmas/stream/rtl/fub/axi_write_engine.sv:366-383) -- plus a SIMULATION-ONLY $error inside translate_off (projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:171-181). A caller contract and a sim assertion are not the same thing as an impossible state, so no cell is marked X.</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:156-181</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rows = rd_sram_valid/rd_sram_ready   cols = </t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): occupancy counts only ACCEPTED beats.</t>
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these three. wr_size and the write side cannot prevent this: the advance is gated on !rd_empty ALONE, never on whether rd_size fits. The alloc side is a separate FIFO with its own pointers (projects/components/dmas/stream/rtl/fub/stream_alloc_ctrl.sv:92, :141) and does not constrain this cone.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: rd_valid &amp; not_empty &amp; size_gt_avail</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      rd_valid &amp; not_empty &amp; size_gt_avail</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>space_free accounting chain (read side)</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/stream_alloc_ctrl.sv:141, projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:310-316, projects/components/dmas/stream/rtl/fub/sram_controller.sv:257-267</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>The 2-flop stage is the 100 MHz timing closure for the 8-channel arbitration cone; false-pathing it was rejected because a stale grant handshake could latch the wrong channel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>stage</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>expression / register</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>staleness</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>alloc_ctrl</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>space_free = DEPTH - (wr_ptr - rd_ptr)</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>combinational</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>sram_controller_unit</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>registered once</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>1 cycle</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>sram_controller wrapper</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>registered again (axi_rd_alloc_space_free port)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>2 cycles total</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>axi_read_engine</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>w_space_ok compares the stale view</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>safe: reservations only SHRINK the stale view</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>drain occupancy advance  (wr_ptr += 1)</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:184</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>.wr_valid(axi_rd_sram_valid &amp;&amp; axi_rd_sram_ready)   [data beat lands in the channel FIFO -&gt; data_available += 1]</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = rd_sram_valid/rd_sram_ready   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at (1,1): occupancy counts only ACCEPTED beats.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="9" t="inlineStr">
+      <c r="B76" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B54" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="B77" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B55" s="11" t="n">
+      <c r="B78" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B56" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B79" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: rd_sram_valid &amp; rd_sram_ready</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
         <is>
           <t>drain reserve advance  (rd_ptr += rd_size)</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D84" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:97-105</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>advance = rd_valid &amp;&amp; rd_ready &amp;&amp; !r_rd_empty   [rd_valid = axi_wr_drain_req (fires on AW handshake); rd_ready = !empty; advances by the FULL rd_size]</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t xml:space="preserve">rows = drain_req/rd_empty   cols = </t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="7" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>CHECK BY INSPECTION: Single 1-cell at (1,0). DANGER cell: the advance is gated only on not-EMPTY, not on size&lt;=available - a reservation larger than the real occupancy makes rd_ptr overshoot wr_ptr and the wrap-corrected count reads ~DEPTH FOREVER (permanent corruption, all-channel freeze). A sim-only $error at projects/components/dmas/stream/rtl/fub/stream_drain_ctrl.sv:172-181 fires at the bad reservation; the write engine's w_effective_avail pipeline is the synthesis-side guarantee the reservation is never oversized.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>AXES: not derived -- axis equations and citations missing (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see [[STREAM-KMAP]])</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="9" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: not stated -- this map is a SLICE with no sufficiency argument (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="9" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>00</t>
         </is>
       </c>
-      <c r="B69" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="9" t="inlineStr">
+      <c r="B92" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="9" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B70" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="B93" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="9" t="inlineStr">
+      <c r="B94" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B72" s="11" t="n">
+      <c r="B95" s="11" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="6" t="inlineStr">
         <is>
           <t>DERIVED MINIMAL SOP: drain_req &amp; !rd_empty</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="13" t="inlineStr">
         <is>
           <t>VERDICT: NOT CHECKED -- supply rtl_sop= to diff the RTL against the derived cover</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
         <is>
           <t>axi_wr_drain_data_avail contract (write side)</t>
         </is>
       </c>
-      <c r="D77" s="5" t="inlineStr">
+      <c r="D100" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/sram_controller_unit.sv:282-307</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="7" t="inlineStr">
         <is>
           <t>BUG FIX (all-channel deadlock): the double-count let the write engine size a burst against beats that did not exist -&gt; over-drain -&gt; permanent occupancy corruption -&gt; stall at the head of the shared in-order W-phase FIFO froze all 8 channels (slow_producer profile). See projects/components/dmas/stream/known_issues/resolved/sram_drain_bridge_double_count.md. Excluding skid beats is conservative-safe: it can only delay an AW, never over-issue one.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>rule</t>
         </is>
       </c>
-      <c r="B79" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>detail</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>avail = drain_ctrl occupancy ONLY</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>assign axi_wr_drain_data_avail = drain_data_available; (w_count of the drain virtual FIFO)</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>bridge_occupancy is EXCLUDED</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B104" s="4" t="inlineStr">
         <is>
           <t>a beat in the latency-bridge skid is still counted by drain_ctrl (its rd_ptr only moves on drain_req), so adding bridge_occupancy counted it TWICE</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="4" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>registered once more at the wrapper</t>
         </is>
       </c>
-      <c r="B82" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/fub/sram_controller.sv:257-267 -&gt; the write engine sees a 2-cycle-stale view and compensates with w_effective_avail</t>
         </is>

--- a/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
+++ b/projects/components/dmas/stream/docs/stream_signal_contracts.xlsx
@@ -978,12 +978,12 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>axi4_master_rd_mon</t>
+          <t>axi4_master_rd_monlite</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>The descriptor master is wrapped by an axi4_master_rd_mon inside scheduler_group_array; stream_core defaults its error/timeout/compl/threshold/debug cones OFF (perf-only) for FPGA fit.</t>
+          <t>The descriptor master is wrapped by an axi4_master_rd_monlite inside scheduler_group_array; stream_core defaults its error/timeout/compl/threshold/debug cones OFF (perf-only) for FPGA fit.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1008,7 +1008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1024,47 +1024,47 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>stream_core monitor gating + block_ready (projects/components/dmas/stream/rtl/macro/stream_core.sv, rtl/amba/axi4/axi4_master_rd_mon.sv, rtl/amba/axi4/axi4_master_wr_mon.sv, rtl/amba/monitor/axi_monitor_base.sv)</t>
+          <t>stream_core monitors: no gating, drop-and-count (projects/components/dmas/stream/rtl/macro/stream_core.sv, rtl/amba/axi4/axi4_master_rd_monlite.sv, rtl/amba/axi4/axi4_master_wr_monlite.sv, rtl/amba/monitor/axi_monitor_lite.sv)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The data-path AXI masters run through axi4_master_rd_mon / axi4_master_wr_mon wrappers. The monitor's block_ready is ANDed into the fub-side AR/AW ready, so a saturated monitor table THROTTLES the engines instead of losing transactions - and the saturation-recovery contract guarantees it un-throttles.</t>
+          <t>The data-path AXI masters run through axi4_master_rd_monlite / axi4_master_wr_monlite (axi_monitor_lite, since 2026-09-26). The lite never touches the traffic it watches: there is no block_ready and the core's fub-side ready is the wrapper's ready, verbatim. Capacity pressure is COUNTED instead of applied -- a command that finds no free table entry is refused (counted, its beats then report as orphans) and an event the monbus cannot take is dropped (counted, the count reported as Error/EVENT_DROPPED). The full monitor's block_ready contract and its saturation-recovery margin no longer exist in this design; they are on the axi_monitor_base page.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>fub_axi_arready gate  (read datapath)</t>
+          <t>fub_axi_arready pass-through  (read datapath)</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/axi4/axi4_master_rd_mon.sv:496-480</t>
+          <t>rtl/amba/axi4/axi4_master_rd_monlite.sv:190</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>fub_axi_arready = w_core_fub_axi_arready &amp; (w_block_ready | ~cfg_monitor_enable)   [identical shape for AW: rtl/amba/axi4/axi4_master_wr_mon.sv:482-483]</t>
+          <t>.fub_axi_arready (fub_axi_arready)   -- the core's ready is the port's ready, no monitor term [identical for AW: rtl/amba/axi4/axi4_master_wr_monlite.sv:206]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>rows = core_ready/block_ready   cols = mon_enable</t>
+          <t xml:space="preserve">rows = core_ready/mon_enable   cols = </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Zero only where core_ready=0 or (block_ready=0 AND mon_enable=1). The mon_enable=0 column must equal core_ready verbatim - a DISABLED monitor never stalls the datapath. A 0 at (1,1,1) would be a monitor stalling while claiming capacity.</t>
+          <t>CHECK BY INSPECTION: Equals core_ready in every cell. The mon_enable column is drawn to make the point: nothing the monitor knows (enable, table state, monbus backpressure) reaches this handshake. The old full-monitor map had a third axis, block_ready, and a 0 at (core_ready=1, block_ready=0, mon_enable=1); that cell is gone with the term.</t>
         </is>
       </c>
     </row>
@@ -1078,19 +1078,14 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: these three. The AR payload (addr/len/id/user) rides the same handshake but cannot affect whether it completes; the monitor's table contents reach this cone only through block_ready, which is already an axis.</t>
+          <t>DEPENDS ONLY ON: core_ready alone. The lite has no path from its table or its output queue to any AXI handshake -- that is the design rule (vault/handbook/design/observers-do-not-drive.md).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -1103,9 +1098,6 @@
       <c r="B12" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
@@ -1116,9 +1108,6 @@
       <c r="B13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C13" s="10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
@@ -1129,9 +1118,6 @@
       <c r="B14" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="11" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
@@ -1142,21 +1128,18 @@
       <c r="B15" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C15" s="10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>DERIVED MINIMAL SOP: core_ready &amp; !mon_enable  |  core_ready &amp; block_ready</t>
+          <t>DERIVED MINIMAL SOP: core_ready</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>RTL AS WRITTEN:      core_ready &amp; block_ready  |  core_ready &amp; !mon_enable</t>
+          <t>RTL AS WRITTEN:      core_ready</t>
         </is>
       </c>
     </row>
@@ -1170,33 +1153,33 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>w_block_ready  (monitor capacity)</t>
+          <t>table refusal  (lite capacity)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/monitor/axi_monitor_base.sv:697-701</t>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:334</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>block_ready = (MAX_TRANSACTIONS &gt; BLOCK_MARGIN) ? (active_count &lt; MAX_TRANSACTIONS - BLOCK_MARGIN) : 1'b1   [vars: max_gt_margin (param, compile-time), count_below (comparator)]</t>
+          <t>w_refused = cmd_hs &amp;&amp; !w_have_free   [a command that finds no free entry is counted in refused_count and NOT tracked; its data/response beats then surface as DATA_ORPHAN / RESP_ORPHAN errors naming it]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">rows = max_gt_margin/count_below   cols = </t>
+          <t xml:space="preserve">rows = cmd_hs/have_free   cols = </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: block_ready follows count_below whenever the table is big enough to carry a margin; degenerate tables never block. POLARITY is the loaded gun here: 1 = proceed. The inverted pre-fix polarity deadlocked every upstream handshake at reset.</t>
+          <t>CHECK BY INSPECTION: One cell: a handshake with a full table. The command still completes on the bus (nothing gates it); the monitor loses the entry, says so (rtl/amba/monitor/axi_monitor_lite.sv:783), and the orphan errors that follow name the id.</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1193,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>DEPENDS ONLY ON: these two. max_gt_margin is a compile-time comparison of two localparams and count_below folds the whole active_count vs MAX_TRANSACTIONS-BLOCK_MARGIN comparison into one term; nothing else in the monitor reaches this assign.</t>
+          <t>DEPENDS ONLY ON: these two. have_free is the OR of the free-slot mask; the id, address and length of the command do not enter the decision.</t>
         </is>
       </c>
     </row>
@@ -1227,8 +1210,8 @@
           <t>00</t>
         </is>
       </c>
-      <c r="B29" s="11" t="n">
-        <v>1</v>
+      <c r="B29" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1237,8 +1220,8 @@
           <t>01</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
-        <v>1</v>
+      <c r="B30" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -1247,8 +1230,8 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B31" s="11" t="n">
-        <v>1</v>
+      <c r="B31" s="10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1257,21 +1240,21 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B32" s="10" t="n">
-        <v>0</v>
+      <c r="B32" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>DERIVED MINIMAL SOP: !max_gt_margin  |  count_below</t>
+          <t>DERIVED MINIMAL SOP: cmd_hs &amp; !have_free</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>RTL AS WRITTEN:      !max_gt_margin  |  count_below</t>
+          <t>RTL AS WRITTEN:      cmd_hs &amp; !have_free</t>
         </is>
       </c>
     </row>
@@ -1285,515 +1268,584 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>COMPL packet emission  (monitor cfg -&gt; packet class)</t>
+          <t>event loss  (lite monbus backpressure)</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>rtl/amba/monitor/axi_monitor_reporter_compl.sv:52</t>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:627</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>w_events[idx] = trans_table[idx].valid &amp;&amp; !event_reported[idx] &amp;&amp; (state == TRANS_COMPLETE) &amp;&amp; cfg_compl_enable   [inside generate if (ENABLE_COMPL_LOGIC); else compl_valid = 1'b0]</t>
+          <t>w_lost = w_offered - w_take; r_dropped += w_lost   [w_offered = events fired this cycle, w_take = the one the pick could queue; the count is reported as Error/EVENT_DROPPED when the queue next has room and nothing else wants it]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>rows = build_compl/use_mon   cols = cfg_compl/is_complete</t>
+          <t xml:space="preserve">rows = event_fired/queue_room   cols = </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. Each axis is ONE term with its own equation -- that is the point: two axes resolving to the same signal would be visible here, which is exactly the aliasing defect that shipped. The complement is the slot-leak guard: w_auto_retire = !ENABLE_COMPL_LOGIC || !cfg_compl_enable retires a terminal entry when no packet can ever be emitted, so a runtime-disabled class frees its slot instead of wedging the table (rtl/amba/monitor/axi_monitor_reporter.sv:496-497). VERDICT READS 'DIFFERS' ON PURPOSE -- and it is the finding. The derived cover drops use_mon: the invariant below makes cfg_compl=1 imply use_mon=1, so the four use_mon=0 &amp;&amp; cfg_compl=1 cells are X and Quine-McCluskey absorbs them. The RTL's use_mon term is therefore REDUNDANT GIVEN THE INVARIANT -- defence in depth, not logic. It is worth keeping (it makes the monitors-off build independent of the CSR plumbing being correct), but this map is what says so, and if the tie-off at CORE:869 were ever removed the term would stop being redundant and start being load-bearing.</t>
+          <t>CHECK BY INSPECTION: A fired event with no queue room is lost and counted. Two events in one cycle lose one even with room (the pick takes one), which this two-axis map folds into event_fired; the arithmetic at :627 is exact.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>AXES: not derived -- axis equations and citations missing (see STREAM TASK-001)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these two plus the per-cycle event count. Which class won the pick (error &gt; timeout &gt; completion &gt; threshold) decides WHICH event was lost, never whether one was.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: event_fired &amp; !queue_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      event_fired &amp; !queue_room</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>VERDICT: IDENTICAL -- the RTL is already minimal</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>COMPL packet emission  (monitor cfg -&gt; packet class)</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:589</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>w_cmp_v = r_e_compl &amp;&amp; w_cmp_en;  w_cmp_en = cfg_compl_enable &amp;&amp; type_allowed(PktTypeCompletion)   [r_e_compl: a clean completion registered from the attribution cycle]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>rows = use_mon/cfg_compl   cols = type_allowed/is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Single 1-cell at all-ones. Each axis is ONE term with its own equation -- two axes resolving to the same signal would be visible here, which is exactly the aliasing defect that shipped. VERDICT READS 'DIFFERS' ON PURPOSE -- and it is the finding: the derived cover drops use_mon, because the invariant below makes cfg_compl=1 imply use_mon=1, so the use_mon=0 &amp;&amp; cfg_compl=1 cells are X and Quine-McCluskey absorbs them. The RTL's use_mon term is REDUNDANT GIVEN THE INVARIANT -- defence in depth, not logic; if the tie-off at CORE:869 were ever removed it would become load-bearing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
         <is>
           <t>AXES</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
         <is>
           <t>axis</t>
         </is>
       </c>
-      <c r="B43" s="8" t="inlineStr">
+      <c r="B60" s="8" t="inlineStr">
         <is>
           <t>defining expression</t>
         </is>
       </c>
-      <c r="D43" s="8" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>cite</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="5" t="inlineStr">
-        <is>
-          <t>build_compl</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>ENABLE_COMPL_LOGIC &lt;- DATA_MON_ENABLE_COMPL_LOGIC (stream_core parameter, default 1'b0)</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:202, :1557</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>use_mon</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>USE_AXI_MONITORS: selects the g_monitors_enabled generate that feeds every int_cfg_*</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:784</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>cfg_compl</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>cfg_compl_enable &lt;- int_cfg_rdeng_mon_compl_enable (= cfg_rdeng_mon_compl_enable when monitors are built)</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:808, :1635</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>is_complete</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>trans_table[idx].state == TRANS_COMPLETE</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>rtl/amba/monitor/axi_monitor_reporter_compl.sv:52</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="14" t="inlineStr">
-        <is>
-          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    use_mon=0 forces cfg_compl to 0: the g_monitors_disabled arm ties every int_cfg_*_enable to 1'b0, so (use_mon=0, cfg_compl=1) is unreachable, not a 0.</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:869</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) build_compl and cfg_compl are INDEPENDENT -- one is a synthesis parameter, the other a runtime CSR bit, and no RTL relates them. Stated because an aliasing defect would show up here as a relation that HAD to exist.</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:202, :808</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    (independent) perf_run is the deliberate exception to the monitors-off tie-off: it passes through to drive the always-on datapath perf window, so monitors-off does NOT zero every cfg signal.</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:883</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>DEPENDS ONLY ON: these four. valid &amp;&amp; !event_reported are per-slot bookkeeping orthogonal to the cfg chain (same expression, rtl/amba/monitor/axi_monitor_reporter_compl.sv:51), and the address-filter path retires separately before this cone (rtl/amba/monitor/axi_monitor_reporter.sv:483-489). The other class enables (error/timeout/perf/threshold) drive their own sub-reporters and cannot change COMPL emission. Per-index i is a loop replication, not a variable of the decision.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E54" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="9" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E55" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C57" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E58" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>DERIVED MINIMAL SOP: build_compl &amp; cfg_compl &amp; is_complete</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>RTL AS WRITTEN:      build_compl &amp; use_mon &amp; cfg_compl &amp; is_complete</t>
+          <t>cfg_compl</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>cfg_compl_enable &lt;- int_cfg_rdeng_mon_compl_enable (= cfg_rdeng_mon_compl_enable when monitors are built)</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:808, :1601</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>type_allowed</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>!cfg_axi_pkt_mask[PktTypeCompletion]</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:559</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>is_complete</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>r_e_compl: last beat (read) or B (write) on a tracked entry with no error recorded</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:589</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="14" t="inlineStr">
+        <is>
+          <t>RELATIONS between axes (these make cells UNREACHABLE -- shown as X, a don't-care, never as 0):</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    use_mon=0 forces cfg_compl to 0: the g_monitors_disabled arm ties every int_cfg_*_enable to 1'b0, so (use_mon=0, cfg_compl=1) is unreachable, not a 0.</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:869</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    (independent) perf_run is the deliberate exception to the monitors-off tie-off: it passes through to drive the always-on datapath perf window, so monitors-off does NOT zero every cfg signal.</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:883</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: these four. The other class enables (error/timeout/threshold) gate their own events in the same registered stage and cannot change COMPL emission. There is no per-slot retire guard any more: the lite frees an entry on its last beat whether or not a packet was emitted, so a runtime-disabled class cannot wedge the table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="9" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C72" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D72" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E72" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>DERIVED MINIMAL SOP: cfg_compl &amp; type_allowed &amp; is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (1 ones, 4 don't-cares -- X cells were free to widen the cover)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>RTL AS WRITTEN:      use_mon &amp; cfg_compl &amp; type_allowed &amp; is_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>VERDICT: DIFFERS -- reconcile: either the RTL carries redundant terms (say why: timing? readability?) or an unstated invariant is doing work, or it is a bug</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>saturation-recovery contract (stream default sizing)</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>rtl/amba/monitor/axi_monitor_base.sv:656-701, rtl/amba/includes/monitor_common_pkg.sv:115-132, projects/components/dmas/stream/rtl/macro/stream_core.sv:125-129</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="7" t="inlineStr">
-        <is>
-          <t>The reopen threshold sits STRICTLY ABOVE the command cap (69 &gt; 68): even a table whose command entries are all permanently in flight recovers block_ready as soon as orphan entries drain. The old flat MAX-3 margin parked the table exactly AT the threshold and never re-asserted (stream_core multi-channel wedge). Undersizing MAX_TRANSACTIONS on purpose (mon_small config) therefore throttles-and-recovers, never deadlocks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>capacity contract (stream default sizing, lite)</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>rtl/amba/monitor/axi_monitor_lite.sv:334, :627, :782-783, projects/components/dmas/stream/rtl/macro/stream_core.sv:125-129</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="inlineStr">
+        <is>
+          <t>The full monitor gated AR/AW through block_ready with a saturation-recovery margin (the stream_core multi-channel wedge was a margin defect). The lite has neither: it never applies pressure, so there is nothing to recover from, and the cost of undersizing MAX_TRANSACTIONS is refused entries whose beats report as orphans -- visible, counted, and never a stall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>expression</t>
         </is>
       </c>
-      <c r="C67" s="3" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>8ch default value</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>MAX_TRANSACTIONS</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>max(16, NUM_CHANNELS * AR_MAX_OUTSTANDING + MON_TRANS_MARGIN)</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>cmd_entry_reserve(MAX)</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>(MAX &gt;= 16) ? 4 : 0</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>command-entry cap (trans_mgr)</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>MAX - reserve</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>BLOCK_MARGIN</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>reserve - 1 (or flat 3 if reserve==0)</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>block threshold</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t>block when active_count &gt;= MAX - margin</t>
-        </is>
-      </c>
-      <c r="C72" s="4" t="inlineStr">
-        <is>
-          <t>&gt;= 69</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>reopen threshold</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>re-assert when active_count &lt; MAX - margin</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="inlineStr">
-        <is>
-          <t>&lt; 69</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>table entries</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>MAX_TRANSACTIONS (no command-entry reserve)</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>on a full table</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>refuse the command: refused_count += 1, no stall</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>counted</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>on a full monbus queue</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>drop the event: dropped_count += lost, reported as EVENT_DROPPED</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>counted</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
         <is>
           <t>monitor enable tie-off (build-level gate)</t>
         </is>
       </c>
-      <c r="D76" s="5" t="inlineStr">
+      <c r="D90" s="5" t="inlineStr">
         <is>
           <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:641-732</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>e.g. projects/components/dmas/stream/rtl/macro/stream_core.sv:660 (enabled branch) vs :715 (tied-off branch). The always-on axi_bus_meter perf buckets survive USE_AXI_MONITORS=0 by design - only the heavy monitors and histograms are gated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>e.g. projects/components/dmas/stream/rtl/macro/stream_core.sv:660 (enabled branch) vs :715 (tied-off branch). The always-on axi_bus_meter perf buckets survive USE_AXI_MONITORS=0 by design - only the monitors and histograms are gated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>USE_AXI_MONITORS</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>int_cfg_*_mon_enable</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B79" s="4">
+      <c r="B93" s="4">
         <f> cfg_*_mon_enable (CSR)</f>
         <v/>
       </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>runtime on/off; wrapper instantiates the monitor (USE_MONITOR=1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="4" t="inlineStr">
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>runtime on/off; wrapper instantiates the lite (USE_MONITOR=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="B80" s="4">
+      <c r="B94" s="4">
         <f> 1'b0 (tied)</f>
         <v/>
       </c>
-      <c r="C80" s="4" t="inlineStr">
-        <is>
-          <t>monitor logic absent, w_block_ready tied 1: bare skid, zero datapath interference</t>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>monitor logic absent: bare skid, zero datapath interference (the lite has none even when built)</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2414,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>axi4_master_rd_mon / axi4_master_wr_mon</t>
+          <t>axi4_master_rd_monlite / axi4_master_wr_monlite</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2835,7 +2887,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:779/:840; rtl/amba/axi4/axi4_master_rd_mon.sv:496-480</t>
+          <t>projects/components/dmas/stream/rtl/macro/stream_core.sv:779/:840; rtl/amba/axi4/axi4_master_rd_monlite.sv:496-480</t>
         </is>
       </c>
     </row>
